--- a/Scraped Tweets - Nigeria/Shola_scope_relevant.xlsx
+++ b/Scraped Tweets - Nigeria/Shola_scope_relevant.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>text</t>
   </si>
@@ -25,9 +25,6 @@
     <t>Either you marry a rich or broke woman, a man will always be a man, the provider of his home, so a woman's money doesn't really mean a thing if the values aren't there, cos with or without her money, you still gotta provide.</t>
   </si>
   <si>
-    <t>Make sure you read "Becoming A Better Man" today.</t>
-  </si>
-  <si>
     <t>Whichever decision the man makes, he's still the provider, he's still gon be the one running majority of the expenses, can't be getting yelled at daily and still getting debit alerts for raising a family. I'd just run madd.</t>
   </si>
   <si>
@@ -37,22 +34,22 @@
     <t>6. Nice guys are weak: she wants a man in his masculine frame, a man who can lead her, a man who has a mind of his own and can make firm decisions and stand on it, not a man who will always bend his rules or change his mind just because he's trying to please her and look perfect.</t>
   </si>
   <si>
-    <t>@Matthew_kings0 @_AsiwajuLerry Even if he's broke, if she doesn't respect him, she's still gone. What's the point you tryna make? When people say make money first, it's not mainly about the women, it's has more to do with getting your priorities right, fighting for your life while doing away with distractions.</t>
-  </si>
-  <si>
-    <t>Read my book "Becoming A Better Man" today.</t>
+    <t>Even if he's broke, if she doesn't respect him, she's still gone. What's the point you tryna make? When people say make money first, it's not mainly about the women, it's has more to do with getting your priorities right, fighting for your life while doing away with distractions.</t>
   </si>
   <si>
     <t>Men need to learn how to say NO often to women without feeling bad about it. Men need to learn how to say NO often to women without having to explain themselves. Men need to learn to always do what's best for them. Don't be a YES man.</t>
   </si>
   <si>
+    <t>My book Becoming A Better Man was created to impact men and help them get better. Seeing it do just that isn't surprising tho, I knew what I dropped for y'all, QUALITY INFORMATION.</t>
+  </si>
+  <si>
     <t>A dramatic rich woman who believes "my money is my money and your money our money", or a submissive broke woman who doesn't bring stress and troubles to your life? She's still got her feminine values, doesn't see marriage as a competition, you'll definitely go for the latter.</t>
   </si>
   <si>
     <t>A feminist who wants equality still doesn't want to go 50/50 with her man, a delusional human being. You don't even want the equality you cry for? You want to earn same salary as a man, and still take from his, while he goes broke, and you get richer than him? Selfish!!!</t>
   </si>
   <si>
-    <t>@PenTitan It's actually hard to believe there are men who know their worth when you as a man don't even respect yourself to start with, it's the lie they tell themselves to feel better while they wallow in nonsense.</t>
+    <t>It's actually hard to believe there are men who know their worth when you as a man don't even respect yourself to start with, it's the lie they tell themselves to feel better while they wallow in nonsense.</t>
   </si>
   <si>
     <t>I've seen women talk about how men are scared to marry rich women because of low self esteem, that's a lie. It's the fact that once a woman gets money, she believes she's independent, doesn't need a man, sees no need to be submissive and becomes rude, and men don't want that.</t>
@@ -61,30 +58,45 @@
     <t>Date submissive women who are respectful and want to be led, instead of dating rude and confused modern women that you'd have to force into something they think it's slavery and reduces them from being humans.</t>
   </si>
   <si>
-    <t>You need to always put your feelings aside when it comes to going after what you want. When it's convenient for you, work. When it's inconvenient, work. That's what makes you a man, the fact that you can always put your feelings aside &amp;amp; still get the job done. Nothing comes easy.</t>
+    <t>You need to always put your feelings aside when it comes to going after what you want. When it's convenient for you, work. When it's inconvenient, work. That's what makes you a man, the fact that you can always put your feelings aside &amp; still get the job done. Nothing comes easy.</t>
+  </si>
+  <si>
+    <t>When we say leave relationship alone when you're broke, it doesn't necessarily mean you can't attract women, or you gotta use money to get women. It's simply you putting yourself first, fighting for your life and against poverty, creating value and doing away with distractions.</t>
+  </si>
+  <si>
+    <t>Til you go steal outside and get caught, end up in jail, while she's free getting smashed by other guys. That isn't love, it's f00lishness.</t>
   </si>
   <si>
     <t>Imagine a man claiming to be an independent man, you see how stupidd it looks? That's how stupidd it looks when I see a woman say "I'm an independent woman". I mean, you are an adult, it is your duty to take care of yourself, so you're just doing the norms. Nothing special.</t>
   </si>
   <si>
+    <t>Every woman claims not to wear revealing clothes for men, but to feel good about themselves. Until a friend of hers visits her matrimonial home dressed to feel good about herself as well and all of a sudden she'd claim she wants to steaI her man.</t>
+  </si>
+  <si>
     <t>3. Nice guys aren't every girl's crush: women love to have men who other women want, men who get chased by other women, men who have options. Nice guys live in scarcity while the female nature works differently, her nature says "if he's wanted by other women, I want him too".</t>
   </si>
   <si>
+    <t>Over 2,600 men have been impacted by my book "Becoming A Better Man", it remains the best selling book in the country since it dropped. Go get your copy too, for just N7,000 on or you send me a DM.</t>
+  </si>
+  <si>
     <t>He asked her out and she started with the billing without even giving him a YES or NO. Men are waking up, good times👑</t>
   </si>
   <si>
     <t>When I see a man and a woman needs financial help, I'd rather help the man if I can only help one person, men are more appreciative. Can't give someone my hard earned money only to see them tweeting shitt about how worthless the money is or using it as a TikTok challenge.</t>
   </si>
   <si>
-    <t>A man who's not ready to grow will always be scared of what people will say.</t>
-  </si>
-  <si>
     <t>Ask women "why are you broke?" and they'd tell you it's because they don't have a boyfriend. Men are really suffering.</t>
   </si>
   <si>
+    <t>This is how you deal with shameIess women, a king in my book👑</t>
+  </si>
+  <si>
     <t>A desperate man will always: - Double text a woman. - Use money to buy affection. - Apologize when she's wrong. - Beg a woman to stay in his life. - Endure the toxicity coming from the woman he's with. - Displease himself to please a woman. - Be a YES MAN. Don't be that guy.</t>
   </si>
   <si>
+    <t>Kings, If your pocket is bigger than that of your siblings, try to uplift them to a point where they all become financially independent. Don't feel proud to be the only/most successful person in your family. The goal is to save the family, not to compete with them.</t>
+  </si>
+  <si>
     <t>Y'all finished men are the problem. You're the enablers of all these bs these women be doing. You don't know when to let go of these women most especially when they're not acting right, you don't respect yourself, you position yourself to be used and pressured. Finished men!!!</t>
   </si>
   <si>
@@ -94,6 +106,24 @@
     <t>Men, nothing will ever be given to you, everything is going to be earned. If you don't go out there and put in the work, you definitely will be without nothing.</t>
   </si>
   <si>
+    <t>"What attractive features do you like in a guy?" That's an unnecessary question to ask a lady #MenWithGame</t>
+  </si>
+  <si>
+    <t>Also, your options of women increases the more valuable you become. You're a man, you still got time, a lot of it. Your prime race begins in your 30s, men age like wine, so there's really no reason to rush, you ain't losing out at the end. Build first.</t>
+  </si>
+  <si>
+    <t>The only females that come through for me are my sisters. I don't even share my problems with women who aren't family to start with.</t>
+  </si>
+  <si>
+    <t>There is a finished man out there working so hard to get rich so he can get that chic that rejected him, seek help man!!!</t>
+  </si>
+  <si>
+    <t>Most powerful thing is self respect. Never lose it for anyone.</t>
+  </si>
+  <si>
+    <t>And the only time nice guys get to go straight to the point, you'd hear "a princess like you shouldn't be replying dms without getting credit alerts, you look too beautiful and deserve to be paid for every reply you give, send your account details please" and he then gets used.</t>
+  </si>
+  <si>
     <t>This is a girl who got him nothing for valentine, and she claimed it's only during men birthdays that a woman should gift her man, valentine is for women. He's such a finished man.</t>
   </si>
   <si>
@@ -106,12 +136,27 @@
     <t>A girl who can't afford to buy skateboard will tell a guy who drives Camry "look at what you're driving" and he'd feel ashamed. Some will even say "the guys that carry me drive bigger cars and are above your level". A girl who is obviously below your class. Women are audacious.</t>
   </si>
   <si>
+    <t>It's not really about the woman, but you. You need the level up. Create purpose, gain financial stability, do it for yourself. Relationship can come later.</t>
+  </si>
+  <si>
+    <t>As a broke man who's yet to figure life out, leave relationship alone, it isn't running anywhere. Go and fight poverty, get your priorities right.</t>
+  </si>
+  <si>
+    <t>Nice guys are just horny guys without options who have a lot of time(close to jobless) and lack self respect.</t>
+  </si>
+  <si>
     <t>4. Nice guys don't go straight to the point: nice guys find it hard to express themselves so it ends up looking like they don't know what they want. But you see bad guys, even if he doesn't want you, maybe he just wants sex, he'd say it confidently. Bad guys are that intentional.</t>
   </si>
   <si>
     <t>5. Nice guys are stalkers, too clingy: girls love attention a lot, so lack of attention will always make her come to you. But once she gets that from you, they see no need to chase you anymore. And that's where nice guys always lose it because they're always too available.</t>
   </si>
   <si>
+    <t>It's your purpose first, purpose over relationship. Never forget that.</t>
+  </si>
+  <si>
+    <t>Hustle for yours. Grind for yours. Stop looking for another man to come save you.</t>
+  </si>
+  <si>
     <t>The guy had to go to her house to apologize, he begged for long and even gave her more money. That's obviously manipulation. This is a two and half year relationship. All this for a girl who was cheating on him as at then.</t>
   </si>
   <si>
@@ -121,34 +166,115 @@
     <t>Reasons you scared of losing her. - You live in scarcity and don't have your options open. - You're scared of being alone. - You've invested too much. - You're insecure; you think less of yourself believing you don't deserve her, thinking she's above your class.</t>
   </si>
   <si>
+    <t>Impress women? You think I'd go to the gym to feel pain on a daily just to impress women? It's self development to me, it's for me, it's therapy to me. Y'all funny asf.</t>
+  </si>
+  <si>
+    <t>Unless you're a rich guy, getting a girl pregnant when you're broke and not ready can halt everything and flip your life upside down. You'd most likely live an average life for the rest of your life, and mess up your journey. You gotta be careful.</t>
+  </si>
+  <si>
     <t>Simps are dangerous to themselves, family, friends, the society in whole. They don't mind selling their friends out or selling their father's house to please these women.</t>
   </si>
   <si>
+    <t>Real life simp stories that was shared on my space on Saturday. 1. A guy got his girl val gift, she then blocked him cos another guy bought her friend an iPhone 14, saying he knows she's been wanting to change her iPhone X all along. The guy came apologizing to get unblocked.</t>
+  </si>
+  <si>
     <t>No matter how much you have, there's always going to be a bigger simp that will outbid you. If you spend 500k weekly to keep her, there's a simp somewhere willing to buy her a car and the latest iPhone to get her attention, and your cheap gf won't think twice before dumping you.</t>
   </si>
   <si>
     <t>There's a finished man somewhere hustling so hard to raise money so he can send the girl he's dating monthly allowance again, save yourself the stress man. Don't do it.</t>
   </si>
   <si>
+    <t>Don't joke with relationships with quality people, they will take you where money and talent can't.</t>
+  </si>
+  <si>
+    <t>The main problem isn't from the people who constantly disrespect you, but from you who let them get comfortable disrespecting you. Shows that you have zero self respect. No one will respect you if you don't respect yourself.</t>
+  </si>
+  <si>
     <t>I've had women I loved so much and I still let go. Do I regret it? No. Do I miss them? Sometimes, yes. Do I show it? No. You really need to have control over your feelings so you don't end up looking stupid.</t>
   </si>
   <si>
     <t>Take care of home first before impressing the streets. The streets are quick to forget and they don't care about you.</t>
   </si>
   <si>
-    <t>@bossladyveevee All I see here is you trying to dodge accountability.</t>
-  </si>
-  <si>
-    <t>@kizito4you He has nothing to prove, he saw he girl he likes, who showed interest first, she's single to him even if she got a man, she's in the position to either accept him or turn him down. It's that simple.</t>
+    <t>How do you expect people to believe in something you yourself don't believe in? They don't even see the picture you're seeing, you're the problem. Most people only believe in results, not visions, so only you got you. Why fail yourself? With self belief, anything is possible.</t>
+  </si>
+  <si>
+    <t>Some days, just go outside, talk to new women, exchange contacts, improve your social skills, you don't necessarily have to call them after.</t>
+  </si>
+  <si>
+    <t>Some of you been calling your parents names for some likes and RTs, you really don't know how stvpid you look honestly. A condom could have prevented that if they knew you'd end up embarrassing them for clout on the internet where nobody gives a fvck about you and your family.</t>
+  </si>
+  <si>
+    <t>2. There's a guy always spoiling his girl, but on different occasions like when his card failed, or he was unable to transfer money to people, he normally call his girl to help with it, that he'd pay her back, and he definitely will. The times he forgot to pay back,</t>
   </si>
   <si>
     <t>There's nothing you'd need a female friend for that you can't get from a male friend unless you clapping those cheeks. More reason I don't keep female friends unless we got a thing or we're doing business together. I'm okay with the male friends I got.</t>
   </si>
   <si>
+    <t>If you want to be happy for the rest of your life, learn to love yourself, learn to prioritize you, learn to say NO, learn to mind your business, learn not to care too much and lastly, understand that you don't need everybody to like you. Stay dangerous.</t>
+  </si>
+  <si>
+    <t>Lol do it more often, it will leave. Also, I've never seen any man get beaten for approaching a woman respectfully before, and rejection is normal, you win some, you lose some, so there's really nothing to worry about.</t>
+  </si>
+  <si>
+    <t>Better days are coming my man🙏🏻</t>
+  </si>
+  <si>
     <t>Nice guys always finish last.</t>
   </si>
   <si>
-    <t>@MindOfHeadking Fact, a woman who doesn't set boundaries when it comes to being accessible to other men shouldn't be taken seriously.</t>
+    <t>What tf are you doing with your life man? I thought you said you wanna be great? But you don't act like it. You wake up late, you don't study, you don't workout, you do nothing to better yourself. You're not ready man, &amp; no one's going to feel sorry for you when you don't get it.</t>
+  </si>
+  <si>
+    <t>Stay safe tomorrow, don't let them kiII you, there's no justice in Nigeria, and the country itself isn't worth dying for. Remember EndSARS victims? No justice til now, lost their lives for nothing. On your way to the polling unit and while you're there, your safety first.</t>
+  </si>
+  <si>
+    <t>Also, don't be empty, be valuable too, if not, they'll distance themselves from you. No one loves to be around people who just take from them. It's more healthy when you pour into people who are pouring into you.</t>
+  </si>
+  <si>
+    <t>They won't cut off Dangote if he was their friend, they won't cut me off if I was their friend too. It's democracy and it's ok for people to view things differently. Your friends don't rate you, you're not valuable. Go create value for yourself.</t>
+  </si>
+  <si>
+    <t>Ade is a finished man.</t>
+  </si>
+  <si>
+    <t>The reasons why your long term friends are cutting you off cos of your political stand is because you're not valuable, they don't rate you. Go work on yourself.</t>
+  </si>
+  <si>
+    <t>You sent her a message, it took her 3 days to reply you, then you desperately replied her as soon as you saw her message with the speed of light, you're a finished man. Seek help!!!</t>
+  </si>
+  <si>
+    <t>Social media has made a lot of people develop low self esteem, love themselves less, become impatient over time. Don't get caught up in comparing yourself to what you see on it. People only show you what they want you to see. Focus on your own journey and what makes you happy.</t>
+  </si>
+  <si>
+    <t>And just like that he just got himself a laptop, a man who runs barefooted will definitely get gifted shoes before a man who begs people for shoes. Play your part first. Blessings Sarki 👑</t>
+  </si>
+  <si>
+    <t>She saw the first text, she's not busy, she doesn't rate you. Don't double text her.</t>
+  </si>
+  <si>
+    <t>Also, The reason why they're threatening you with "if you need help, don't come to me, I'll curse you" is because you beg too much, you're not going hard for you enough, now GET BACK TO WORK. Enough of the disrespect.</t>
+  </si>
+  <si>
+    <t>Some days, it will look like it's soap, while some days, it'd look like you and God got beef. More reason why you should always show up everyday, so you don't miss out on those good days. Keep grinding!!!</t>
+  </si>
+  <si>
+    <t>Big thank you to who chose to tutor these selected people for free, let's continue to do great things my man.</t>
+  </si>
+  <si>
+    <t>The guy who got a laptop on my page today only got it because he started learning HTML &amp; CSS with his phone. His efforts earned him the laptop, he didn't wait til he got a laptop to better himself. Start with what you have, you'd find a way, help will come, people are watching.</t>
+  </si>
+  <si>
+    <t>We build men and push them to get better here👑</t>
+  </si>
+  <si>
+    <t>These men always think it's about being a demon lmaooo maybe we need to start putting our women on camera so they can see how we deal in real life, and how we get a lot of women even after not giving a fvck on the internet.</t>
+  </si>
+  <si>
+    <t>Meeting women in person or chatting with women online? What's your best means of approach? And why?</t>
+  </si>
+  <si>
+    <t>Fact, a woman who doesn't set boundaries when it comes to being accessible to other men shouldn't be taken seriously.</t>
   </si>
   <si>
     <t>The respectful, well mannered rich women will never complain about men not moving to them. It's always the delusional ones with bad attitudes.</t>
@@ -157,7 +283,13 @@
     <t>Men and women friendships are mostly parasitic, one sided and beneficial to women only. In most cases, they use you for emotional and financial support, chat buddy to kiII boredom, while you get nothing in return. You're definitely getting used in the process.</t>
   </si>
   <si>
-    <t>@Michaelizuagwu "If you skip the building phase and go after women, women will skip you"</t>
+    <t>We're getting there already. One thing is certain, men will never be on the losing side.</t>
+  </si>
+  <si>
+    <t>"If you skip the building phase and go after women, women will skip you"</t>
+  </si>
+  <si>
+    <t>These type of men are the worst, zero self awareness, weak observations too.</t>
   </si>
   <si>
     <t>Men, how do you comfortably borrow money from women? Some of you even end up not paying back. Ridiculous!</t>
@@ -166,28 +298,103 @@
     <t>You can't enter a girl's DM like this and still complain she dated you for your money, what were you expecting? You brought it upon yourself. Learn Game Kings!!!</t>
   </si>
   <si>
+    <t>Fact, I think one of the reasons I prefer meeting women in person is for the fact that you can always be spontaneous with it, read body language easily, you can even tell if a woman is feeling you just from having a 10-20 minutes talk.</t>
+  </si>
+  <si>
+    <t>6. Go outside, meet new women.</t>
+  </si>
+  <si>
+    <t>When trying to make friends and build a circle, choose men who fit not just in your present, but in your future too.</t>
+  </si>
+  <si>
+    <t>Nigerian men are finished. Majority got no game obviously.</t>
+  </si>
+  <si>
     <t>Every woman has transport fare if she really wants to see you. You only send transport fare to women who aren't craving to see you.</t>
   </si>
   <si>
-    <t>@Alan_yournextbf I have enough friends, why should I add you to my circle? You gotta be giving what my gees can't give then. Orgasm or we doing business, or you leave me alone madam. Female friendships are mostly parasitic. It's never favorable for men. The see finish that comes with it is worse.</t>
+    <t>You need to start taking your life more seriously.</t>
+  </si>
+  <si>
+    <t>I have enough friends, why should I add you to my circle? You gotta be giving what my gees can't give then. Orgasm or we doing business, or you leave me alone madam. Female friendships are mostly parasitic. It's never favorable for men. The see finish that comes with it is worse.</t>
   </si>
   <si>
     <t>For your sanity, Choose a woman who chooses you.</t>
   </si>
   <si>
+    <t>You're not a therapist, you're not Jesus, save your money instead of trying so hard to save these women.</t>
+  </si>
+  <si>
+    <t>What is the best piece of advice you have ever received and how did it impact your life?</t>
+  </si>
+  <si>
+    <t>I prefer talking at night tho, I rarely call women during the day. The atmosphere, the fact that they're most likely done with their job for the day, the vibe is always different.</t>
+  </si>
+  <si>
+    <t>Wait, this is the fourth screenshot I'm seeing tonight about women not having clothes to wear out. Scary times.</t>
+  </si>
+  <si>
     <t>Kings, Never be ashamed for being unable to carry financial burdens which isn't yours, learn to put entitled women in their space. They should be on the street either carrying a gvn or a bowl, stick and black shade on begging to make ends meet.</t>
   </si>
   <si>
+    <t>She was always posting on her WhatsApp status saying "if you borrow money from your partner, learn to pay back" which is disrespectful. Fast forward to few years after he's been funding her and giving her money even without asking, She needed about 150k to be precise</t>
+  </si>
+  <si>
+    <t>They are dangerous to these women too, they'll go any length to get them.</t>
+  </si>
+  <si>
     <t>It's the girls caption for me, these men deserve to be used tho. Use them!!!</t>
   </si>
   <si>
-    <t>How I went from being verified with over 460k followers on here, to getting reported for tweeting my opinions &amp;amp; helping men grow, to coming back on the app twice, losing both accounts again, to opening this, the fourth account &amp;amp; Elon Musk came thru. 100k followers, 900k to go❤️</t>
+    <t>This is very valid, it shows she wants it as much as you want it. Mutual satisfaction.</t>
+  </si>
+  <si>
+    <t>4. Unfollow accounts that tweets about sex and nudity at all time. Yeah it helps, you really need to control what you see.</t>
+  </si>
+  <si>
+    <t>People are not jobless woman.</t>
   </si>
   <si>
     <t>When you're wrong, you apologize. When she's wrong, you still apologize. In her head, she's like; "Why did he apologize even when I'm the one who's wrong? He's obviously scared to lose me, maybe I'm too good for him, I think I need to leave him and find someone who's better."</t>
   </si>
   <si>
-    <t>@ThemancalledEm1 They deserve to be used, honestly.</t>
+    <t>If you're wanting to do things only when it's convenient for you, you'll leave a lot of things undone and it will really be hard for you to see results when trying to attain success. Learn to gain control over your emotions.</t>
+  </si>
+  <si>
+    <t>I really love this, the Career Talk space we had on Saturday keeps helping our kings grow and get busy, it was an eye opener for many and the results been coming so quick. Rooting for y'all.</t>
+  </si>
+  <si>
+    <t>Fvck pick up lines bro, women aren't that hard. You'd end up looking like a joke.</t>
+  </si>
+  <si>
+    <t>This same saying has ruined a lot of people's life.</t>
+  </si>
+  <si>
+    <t>The fear of screenshot lol, as long as you're not fooling yourself in the dm or simping your way through, anyone is free to screenshot and post whatever they wanna post, that's on them, not you. You just gotta put in your game while texting, that's all.</t>
+  </si>
+  <si>
+    <t>When I see y'all growing, it brings me so much joy. If he can learn it without a laptop, what's your excuse? Let's do more👏🏼👏🏼👑</t>
+  </si>
+  <si>
+    <t>He deserves to be used!!!</t>
+  </si>
+  <si>
+    <t>1. You can always come back from anything. 2. Consistency is key. 3. You only lose when you give up. 4. People can't end what they didn't build, only you have that power. 5. Nobody can stop the movement we've started, the message will definitely go round. Let's do more Kings👑</t>
+  </si>
+  <si>
+    <t>Many got ulterior motives; behind their gestures of kindness is an expectation of receiving something in return, which makes it all fake.</t>
+  </si>
+  <si>
+    <t>They deserve to be used, honestly.</t>
+  </si>
+  <si>
+    <t>Getting too many rejections is a reminder that you have a lot of self development to do, and you're also focusing on the wrong thing. Focus on you til the focus is on you.</t>
+  </si>
+  <si>
+    <t>Moved into a new apartment in January. Been consistent at the gym for 3 months now. Started learning forex, still learning. Made money, even though I'm not satisfied. My family is good. 2023 definitely will be a good year.</t>
+  </si>
+  <si>
+    <t>He didn't plan a link up, felt too comfortable being a chat buddy, too much availability ruined it.</t>
   </si>
   <si>
     <t>A girl with such mindset is enough reason to be a red flag, you know she's damaged already.</t>
@@ -196,10 +403,52 @@
     <t>God didn't create you to be lazy. The Bible says he created you in his own image, meaning you should walk like him, talk like him. It took him 6 days to create heaven and earth, he then rested the 7th day. So, why are you resting when you've not worked at all? Go do something.</t>
   </si>
   <si>
+    <t>You've always watched out for people, you've always put them first before yourself. When will you prioritize yourself?</t>
+  </si>
+  <si>
+    <t>You know what to do, you either reject them or use them.</t>
+  </si>
+  <si>
+    <t>Nobody will care about how rough the journey was, until you win. They only care about the results, not the struggles and sacrifices.</t>
+  </si>
+  <si>
+    <t>Make sure she is feeling you before you tell her how you feel about her.</t>
+  </si>
+  <si>
     <t>All of a sudden, she started insulting him, she said she's his girlfriend, she is not meant to give him back the money, that he doesn't deserve to get the money back, went ahead to block him.</t>
   </si>
   <si>
-    <t>@Abimbolacrown11 Tell him 10k is too small, collect more. Use him!!!</t>
+    <t>2. Start now: procrastination is the kiIIer of dreams. You keep saying I'd start tomorrow, forgetting there'd always be another tomorrow. The best time to make that move is NOW. The best time to change your life is NOW. Start small, start inexperienced, start scared, start now.</t>
+  </si>
+  <si>
+    <t>2. Get busy; make sure you're active all through the day. Do something. If needed, learn a skill that keeps you busy, it helps.</t>
+  </si>
+  <si>
+    <t>Not necessarily, if you ain't feeling her enough, you can.</t>
+  </si>
+  <si>
+    <t>Welcome back. Thank you for choosing to save the suffering masses, you'll get what you deserve.</t>
+  </si>
+  <si>
+    <t>Felt bad? If you're feeling her, give her a call.</t>
+  </si>
+  <si>
+    <t>Tell him 10k is too small, collect more. Use him!!!</t>
+  </si>
+  <si>
+    <t>There's no rest for me in this world til I get what I want.</t>
+  </si>
+  <si>
+    <t>Why did you cut out the part where you both went to the hotel after the flex?</t>
+  </si>
+  <si>
+    <t>6 tips on how to end masturbation addiction. 1. Firstly admit to the fact that you're addicted and remorsefully feel the need to quit after thinking through how it's affected you negatively. You've to make that intentional decision, it has more to do with your readiness to quit.</t>
+  </si>
+  <si>
+    <t>3. Set realistic goals and make sure you achieve them within the given timeframe: you first write down your goals, set a timeframe for achieving them, write down things you will need to achieve them, and focus on chasing your goals, you'd get it.</t>
+  </si>
+  <si>
+    <t>Thanks for all you do, thanks for sharing a part of you to improve people lives.</t>
   </si>
 </sst>
 </file>
@@ -557,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -870,6 +1119,421 @@
         <v>61</v>
       </c>
     </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
